--- a/artfynd/A 18825-2025 artfynd.xlsx
+++ b/artfynd/A 18825-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131106811</v>
       </c>
       <c r="B2" t="n">
-        <v>98917</v>
+        <v>98918</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>David Isaksson, Liam Martin, Anders Forsberg</t>
+          <t>Anders Forsberg, Liam Martin, David Isaksson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -803,7 +803,7 @@
         <v>131106810</v>
       </c>
       <c r="B3" t="n">
-        <v>98930</v>
+        <v>98931</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>David Isaksson, Liam Martin, Anders Forsberg</t>
+          <t>Anders Forsberg, Liam Martin, David Isaksson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 18825-2025 artfynd.xlsx
+++ b/artfynd/A 18825-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Forsberg, Liam Martin, David Isaksson</t>
+          <t>David Isaksson, Liam Martin, Anders Forsberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Forsberg, Liam Martin, David Isaksson</t>
+          <t>David Isaksson, Liam Martin, Anders Forsberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 18825-2025 artfynd.xlsx
+++ b/artfynd/A 18825-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131106811</v>
       </c>
       <c r="B2" t="n">
-        <v>98918</v>
+        <v>98919</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>131106810</v>
       </c>
       <c r="B3" t="n">
-        <v>98931</v>
+        <v>98932</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 18825-2025 artfynd.xlsx
+++ b/artfynd/A 18825-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131106811</v>
       </c>
       <c r="B2" t="n">
-        <v>98919</v>
+        <v>98922</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>131106810</v>
       </c>
       <c r="B3" t="n">
-        <v>98932</v>
+        <v>98935</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 18825-2025 artfynd.xlsx
+++ b/artfynd/A 18825-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131106811</v>
       </c>
       <c r="B2" t="n">
-        <v>98922</v>
+        <v>98923</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>131106810</v>
       </c>
       <c r="B3" t="n">
-        <v>98935</v>
+        <v>98936</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 18825-2025 artfynd.xlsx
+++ b/artfynd/A 18825-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131106811</v>
       </c>
       <c r="B2" t="n">
-        <v>98923</v>
+        <v>98925</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>131106810</v>
       </c>
       <c r="B3" t="n">
-        <v>98936</v>
+        <v>98938</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 18825-2025 artfynd.xlsx
+++ b/artfynd/A 18825-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131106811</v>
       </c>
       <c r="B2" t="n">
-        <v>98925</v>
+        <v>98926</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>131106810</v>
       </c>
       <c r="B3" t="n">
-        <v>98938</v>
+        <v>98939</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 18825-2025 artfynd.xlsx
+++ b/artfynd/A 18825-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>David Isaksson, Liam Martin, Anders Forsberg</t>
+          <t>Anders Forsberg, Liam Martin, David Isaksson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>David Isaksson, Liam Martin, Anders Forsberg</t>
+          <t>Anders Forsberg, Liam Martin, David Isaksson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 18825-2025 artfynd.xlsx
+++ b/artfynd/A 18825-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131106811</v>
       </c>
       <c r="B2" t="n">
-        <v>98926</v>
+        <v>98927</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Forsberg, Liam Martin, David Isaksson</t>
+          <t>David Isaksson, Liam Martin, Anders Forsberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -803,7 +803,7 @@
         <v>131106810</v>
       </c>
       <c r="B3" t="n">
-        <v>98939</v>
+        <v>98940</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Forsberg, Liam Martin, David Isaksson</t>
+          <t>David Isaksson, Liam Martin, Anders Forsberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 18825-2025 artfynd.xlsx
+++ b/artfynd/A 18825-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131106811</v>
       </c>
       <c r="B2" t="n">
-        <v>98927</v>
+        <v>98930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>131106810</v>
       </c>
       <c r="B3" t="n">
-        <v>98940</v>
+        <v>98943</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 18825-2025 artfynd.xlsx
+++ b/artfynd/A 18825-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131106811</v>
       </c>
       <c r="B2" t="n">
-        <v>98930</v>
+        <v>98931</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>131106810</v>
       </c>
       <c r="B3" t="n">
-        <v>98943</v>
+        <v>98944</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 18825-2025 artfynd.xlsx
+++ b/artfynd/A 18825-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131106811</v>
+        <v>131106810</v>
       </c>
       <c r="B2" t="n">
-        <v>98931</v>
+        <v>99035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,26 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220093</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>600678</v>
+        <v>600701</v>
       </c>
       <c r="R2" t="n">
-        <v>6974440</v>
+        <v>6974422</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,7 +749,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2025_0366</t>
+          <t>2025_0367</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131106810</v>
+        <v>131106811</v>
       </c>
       <c r="B3" t="n">
-        <v>98944</v>
+        <v>99022</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -811,26 +811,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>220093</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -844,10 +844,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>600701</v>
+        <v>600678</v>
       </c>
       <c r="R3" t="n">
-        <v>6974422</v>
+        <v>6974440</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,7 +874,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2025_0367</t>
+          <t>2025_0366</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 18825-2025 artfynd.xlsx
+++ b/artfynd/A 18825-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -797,6 +802,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106810</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -922,8 +932,17 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106811</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>